--- a/data/excel_config.xlsx
+++ b/data/excel_config.xlsx
@@ -110,7 +110,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -139,7 +139,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -151,6 +150,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -503,31 +508,47 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:B4"/>
+  <dimension ref="A2:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
-    <col width="13.375" bestFit="1" customWidth="1" min="1" max="1"/>
-    <col width="181.875" customWidth="1" min="2" max="2"/>
+    <col width="14.625" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="181.875" customWidth="1" style="18" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="2">
-      <c r="A2" t="inlineStr">
+    <row r="2" ht="42.75" customHeight="1">
+      <c r="A2" s="11" t="inlineStr">
         <is>
           <t>Link_Pathหลัก</t>
         </is>
       </c>
-      <c r="B2" s="12" t="inlineStr">
-        <is>
-          <t>https://muangthaiinsurance.sharepoint.com/:f:/r/sites/MTI-Finance-Budgeting/Shared%20Documents/General/Test%20_%20Shared?d=we3ab3a644ca44098becadf4ca942888c&amp;csf=1&amp;web=1&amp;e=Ib7Uew</t>
+      <c r="B2" s="19" t="inlineStr">
+        <is>
+          <t>https://muangthaiinsurance.sharepoint.com/:f:/r/sites/MTI-Finance-Budgeting/Shared%20Documents/General/Budget%202027_User/1.%E0%B8%9C%E0%B8%B9%E0%B9%89%E0%B8%9A%E0%B8%A3%E0%B8%B4%E0%B8%AB%E0%B8%B2%E0%B8%A3%E0%B8%9D%E0%B9%88%E0%B8%B2%E0%B8%A2?d=w1950642807be4b45bf23d035c4a0f749&amp;csf=1&amp;web=1&amp;e=E2gh8Z</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="12" t="n"/>
+      <c r="B4" s="19" t="n"/>
+    </row>
+    <row r="6">
+      <c r="B6" s="19" t="inlineStr">
+        <is>
+          <t>https://muangthaiinsurance.sharepoint.com/:f:/r/sites/MTI-Finance-Budgeting/Shared%20Documents/General/Budget%202027_User?d=we3ab3a644ca44098becadf4ca942888c&amp;csf=1&amp;web=1&amp;e=RSH8P4</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="42.75" customHeight="1">
+      <c r="B10" s="19" t="inlineStr">
+        <is>
+          <t>https://muangthaiinsurance.sharepoint.com/:f:/r/sites/MTI-Finance-Budgeting/Shared%20Documents/General/Budget%202027_User/1.%E0%B8%9C%E0%B8%B9%E0%B9%89%E0%B8%9A%E0%B8%A3%E0%B8%B4%E0%B8%AB%E0%B8%B2%E0%B8%A3%E0%B8%9D%E0%B9%88%E0%B8%B2%E0%B8%A2?d=w1950642807be4b45bf23d035c4a0f749&amp;csf=1&amp;web=1&amp;e=E2gh8Z</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B2" display="https://muangthaiinsurance.sharepoint.com/:f:/r/sites/MTI-Finance-Budgeting/Shared%20Documents/General/Budget%202027_User/1.%E0%B8%9C%E0%B8%B9%E0%B9%89%E0%B8%9A%E0%B8%A3%E0%B8%B4%E0%B8%AB%E0%B8%B2%E0%B8%A3%E0%B8%9D%E0%B9%88%E0%B8%B2%E0%B8%A2?d=w1950642807be4b45bf23d035c4a0f749&amp;csf=1&amp;web=1&amp;e=E2gh8Z" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B6" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B10" display="https://muangthaiinsurance.sharepoint.com/:f:/r/sites/MTI-Finance-Budgeting/Shared%20Documents/General/Budget%202027_User/1.%E0%B8%9C%E0%B8%B9%E0%B9%89%E0%B8%9A%E0%B8%A3%E0%B8%B4%E0%B8%AB%E0%B8%B2%E0%B8%A3%E0%B8%9D%E0%B9%88%E0%B8%B2%E0%B8%A2?d=w1950642807be4b45bf23d035c4a0f749&amp;csf=1&amp;web=1&amp;e=E2gh8Z" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -548,39 +569,39 @@
     <col width="9.25" bestFit="1" customWidth="1" min="4" max="4"/>
     <col width="10.125" bestFit="1" customWidth="1" min="5" max="6"/>
     <col width="11.5" bestFit="1" customWidth="1" min="7" max="7"/>
-    <col width="18.25" bestFit="1" customWidth="1" style="19" min="8" max="8"/>
+    <col width="18.25" bestFit="1" customWidth="1" style="20" min="8" max="8"/>
     <col width="83.25" bestFit="1" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="1" s="6">
-      <c r="C1" s="16" t="inlineStr">
+      <c r="C1" s="15" t="inlineStr">
         <is>
           <t>การให้สิทธิ์</t>
         </is>
       </c>
-      <c r="D1" s="17" t="n"/>
-      <c r="E1" s="16" t="inlineStr">
+      <c r="D1" s="16" t="n"/>
+      <c r="E1" s="15" t="inlineStr">
         <is>
           <t>ช่วงเวลาการให้สิทธิ์</t>
         </is>
       </c>
-      <c r="F1" s="17" t="n"/>
-      <c r="G1" s="18" t="inlineStr">
+      <c r="F1" s="16" t="n"/>
+      <c r="G1" s="17" t="inlineStr">
         <is>
           <t>Logs</t>
         </is>
       </c>
-      <c r="H1" s="17" t="n"/>
+      <c r="H1" s="16" t="n"/>
       <c r="I1" s="11" t="n"/>
       <c r="J1" s="11" t="n"/>
     </row>
     <row r="2" customFormat="1" s="11">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="12" t="inlineStr">
         <is>
           <t>ลำดับ</t>
         </is>
       </c>
-      <c r="B2" s="13" t="inlineStr">
+      <c r="B2" s="12" t="inlineStr">
         <is>
           <t>Path_ย่อย</t>
         </is>
@@ -610,7 +631,7 @@
           <t>สถานะล่าสุด</t>
         </is>
       </c>
-      <c r="H2" s="20" t="inlineStr">
+      <c r="H2" s="21" t="inlineStr">
         <is>
           <t>Logs_Date</t>
         </is>
@@ -627,42 +648,42 @@
       </c>
       <c r="B3" s="1" t="inlineStr">
         <is>
-          <t>Admin Expense_1083</t>
+          <t>Admin expense_1001</t>
         </is>
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>sangchai.s@muangthaiinsurance.com</t>
+          <t>Sangchai.s@muangthaiinsurance.com</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
         <is>
-          <t>Read Only</t>
-        </is>
-      </c>
-      <c r="E3" s="21" t="inlineStr">
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="F3" s="21" t="inlineStr">
+      <c r="F3" s="22" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
       <c r="G3" s="1" t="inlineStr">
         <is>
-          <t>Read Only</t>
-        </is>
-      </c>
-      <c r="H3" s="22" t="inlineStr">
-        <is>
-          <t>2026-09-24 23:24:22</t>
+          <t>Edit</t>
+        </is>
+      </c>
+      <c r="H3" s="23" t="inlineStr">
+        <is>
+          <t>2026-09-30 15:41:14</t>
         </is>
       </c>
       <c r="I3" s="1" t="inlineStr">
         <is>
-          <t>Granted successfully; ส่งอีเมลสำเร็จไปยัง sangchai.s@muangthaiinsurance.com</t>
+          <t>Cookie หมดอายุ หรือ site_url ผิด (HTTP 403)</t>
         </is>
       </c>
     </row>
@@ -685,31 +706,19 @@
           <t>Edit</t>
         </is>
       </c>
-      <c r="E4" s="21" t="inlineStr">
+      <c r="E4" s="22" t="inlineStr">
         <is>
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="F4" s="21" t="inlineStr">
+      <c r="F4" s="22" t="inlineStr">
         <is>
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="G4" s="1" t="inlineStr">
-        <is>
-          <t>ยกเลิก</t>
-        </is>
-      </c>
-      <c r="H4" s="22" t="inlineStr">
-        <is>
-          <t>2026-09-23 13:51:23</t>
-        </is>
-      </c>
-      <c r="I4" s="1" t="inlineStr">
-        <is>
-          <t>Revoked successfully; ส่งอีเมลสำเร็จไปยัง Chudsada.M@muangthaiinsurance.com</t>
-        </is>
-      </c>
+      <c r="G4" s="1" t="n"/>
+      <c r="H4" s="23" t="n"/>
+      <c r="I4" s="1" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -730,31 +739,19 @@
           <t>Edit</t>
         </is>
       </c>
-      <c r="E5" s="21" t="inlineStr">
+      <c r="E5" s="22" t="inlineStr">
         <is>
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="F5" s="21" t="inlineStr">
+      <c r="F5" s="22" t="inlineStr">
         <is>
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="G5" s="1" t="inlineStr">
-        <is>
-          <t>ยกเลิก</t>
-        </is>
-      </c>
-      <c r="H5" s="22" t="inlineStr">
-        <is>
-          <t>2026-09-23 13:55:05</t>
-        </is>
-      </c>
-      <c r="I5" s="1" t="inlineStr">
-        <is>
-          <t>Revoked successfully; ส่งอีเมลสำเร็จไปยัง Soracha.v@muangthaiinsurance.com</t>
-        </is>
-      </c>
+      <c r="G5" s="1" t="n"/>
+      <c r="H5" s="23" t="n"/>
+      <c r="I5" s="1" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -775,23 +772,15 @@
           <t>Edit</t>
         </is>
       </c>
-      <c r="E6" s="21" t="n">
+      <c r="E6" s="22" t="n">
         <v>46269</v>
       </c>
-      <c r="F6" s="21" t="n">
+      <c r="F6" s="22" t="n">
         <v>46298</v>
       </c>
       <c r="G6" s="1" t="n"/>
-      <c r="H6" s="22" t="inlineStr">
-        <is>
-          <t>2026-09-19 02:44:27</t>
-        </is>
-      </c>
-      <c r="I6" s="1" t="inlineStr">
-        <is>
-          <t>เชื่อมต่อ SMTP ไม่ได้ (SMTPNotSupportedError): STARTTLS extension not supported by server.</t>
-        </is>
-      </c>
+      <c r="H6" s="23" t="n"/>
+      <c r="I6" s="1" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -812,23 +801,15 @@
           <t>Read Only</t>
         </is>
       </c>
-      <c r="E7" s="21" t="n">
+      <c r="E7" s="22" t="n">
         <v>46270</v>
       </c>
-      <c r="F7" s="21" t="n">
+      <c r="F7" s="22" t="n">
         <v>46299</v>
       </c>
       <c r="G7" s="1" t="n"/>
-      <c r="H7" s="22" t="inlineStr">
-        <is>
-          <t>2026-09-19 02:50:14</t>
-        </is>
-      </c>
-      <c r="I7" s="1" t="inlineStr">
-        <is>
-          <t>เชื่อมต่อ SMTP ไม่ได้ (SMTPNotSupportedError): STARTTLS extension not supported by server.</t>
-        </is>
-      </c>
+      <c r="H7" s="23" t="n"/>
+      <c r="I7" s="1" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -849,21 +830,15 @@
           <t>Edit</t>
         </is>
       </c>
-      <c r="E8" s="21" t="n">
+      <c r="E8" s="22" t="n">
         <v>46271</v>
       </c>
-      <c r="F8" s="21" t="n">
+      <c r="F8" s="22" t="n">
         <v>46300</v>
       </c>
       <c r="G8" s="1" t="n"/>
-      <c r="H8" s="22" t="n">
-        <v>46284</v>
-      </c>
-      <c r="I8" s="1" t="inlineStr">
-        <is>
-          <t>เชื่อมต่อ SMTP ไม่ได้ (SMTPNotSupportedError): STARTTLS extension not supported by server.</t>
-        </is>
-      </c>
+      <c r="H8" s="23" t="n"/>
+      <c r="I8" s="1" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n">
@@ -884,21 +859,15 @@
           <t>Edit</t>
         </is>
       </c>
-      <c r="E9" s="21" t="n">
+      <c r="E9" s="22" t="n">
         <v>46272</v>
       </c>
-      <c r="F9" s="21" t="n">
+      <c r="F9" s="22" t="n">
         <v>46301</v>
       </c>
       <c r="G9" s="1" t="n"/>
-      <c r="H9" s="22" t="n">
-        <v>46283</v>
-      </c>
-      <c r="I9" s="1" t="inlineStr">
-        <is>
-          <t>เชื่อมต่อ SMTP ไม่ได้ (SMTPNotSupportedError): STARTTLS extension not supported by server.</t>
-        </is>
-      </c>
+      <c r="H9" s="23" t="n"/>
+      <c r="I9" s="1" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -919,25 +888,15 @@
           <t>Edit</t>
         </is>
       </c>
-      <c r="E10" s="21" t="n">
+      <c r="E10" s="22" t="n">
         <v>46273</v>
       </c>
-      <c r="F10" s="21" t="n">
+      <c r="F10" s="22" t="n">
         <v>46302</v>
       </c>
-      <c r="G10" s="1" t="inlineStr">
-        <is>
-          <t>ยกเลิก</t>
-        </is>
-      </c>
-      <c r="H10" s="22" t="n">
-        <v>46283</v>
-      </c>
-      <c r="I10" s="1" t="inlineStr">
-        <is>
-          <t>เชื่อมต่อ SMTP ไม่ได้ (SMTPNotSupportedError): STARTTLS extension not supported by server.</t>
-        </is>
-      </c>
+      <c r="G10" s="1" t="n"/>
+      <c r="H10" s="23" t="n"/>
+      <c r="I10" s="1" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -958,23 +917,15 @@
           <t>Edit</t>
         </is>
       </c>
-      <c r="E11" s="21" t="n">
+      <c r="E11" s="22" t="n">
         <v>46274</v>
       </c>
-      <c r="F11" s="21" t="n">
+      <c r="F11" s="22" t="n">
         <v>46303</v>
       </c>
       <c r="G11" s="1" t="n"/>
-      <c r="H11" s="22" t="inlineStr">
-        <is>
-          <t>2026-09-19 03:46:40</t>
-        </is>
-      </c>
-      <c r="I11" s="1" t="inlineStr">
-        <is>
-          <t>เชื่อมต่อ SMTP ไม่ได้ (SMTPNotSupportedError): STARTTLS extension not supported by server.</t>
-        </is>
-      </c>
+      <c r="H11" s="23" t="n"/>
+      <c r="I11" s="1" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n">
@@ -995,16 +946,14 @@
           <t>Read Only</t>
         </is>
       </c>
-      <c r="E12" s="21" t="n">
+      <c r="E12" s="22" t="n">
         <v>46275</v>
       </c>
-      <c r="F12" s="21" t="n">
+      <c r="F12" s="22" t="n">
         <v>46304</v>
       </c>
       <c r="G12" s="1" t="n"/>
-      <c r="H12" s="22" t="n">
-        <v>46280</v>
-      </c>
+      <c r="H12" s="23" t="n"/>
       <c r="I12" s="1" t="n"/>
     </row>
     <row r="13">
@@ -1026,23 +975,15 @@
           <t>Edit</t>
         </is>
       </c>
-      <c r="E13" s="21" t="n">
+      <c r="E13" s="22" t="n">
         <v>46276</v>
       </c>
-      <c r="F13" s="21" t="n">
+      <c r="F13" s="22" t="n">
         <v>46305</v>
       </c>
       <c r="G13" s="1" t="n"/>
-      <c r="H13" s="22" t="inlineStr">
-        <is>
-          <t>2026-09-19 03:46:03</t>
-        </is>
-      </c>
-      <c r="I13" s="1" t="inlineStr">
-        <is>
-          <t>Revoked successfully</t>
-        </is>
-      </c>
+      <c r="H13" s="23" t="n"/>
+      <c r="I13" s="1" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n">
@@ -1063,16 +1004,14 @@
           <t>Edit</t>
         </is>
       </c>
-      <c r="E14" s="21" t="n">
+      <c r="E14" s="22" t="n">
         <v>46277</v>
       </c>
-      <c r="F14" s="21" t="n">
+      <c r="F14" s="22" t="n">
         <v>46306</v>
       </c>
       <c r="G14" s="1" t="n"/>
-      <c r="H14" s="22" t="n">
-        <v>46280</v>
-      </c>
+      <c r="H14" s="23" t="n"/>
       <c r="I14" s="1" t="n"/>
     </row>
     <row r="15">
@@ -1094,16 +1033,14 @@
           <t>Read Only</t>
         </is>
       </c>
-      <c r="E15" s="21" t="n">
+      <c r="E15" s="22" t="n">
         <v>46278</v>
       </c>
-      <c r="F15" s="21" t="n">
+      <c r="F15" s="22" t="n">
         <v>46307</v>
       </c>
       <c r="G15" s="1" t="n"/>
-      <c r="H15" s="22" t="n">
-        <v>46280</v>
-      </c>
+      <c r="H15" s="23" t="n"/>
       <c r="I15" s="1" t="n"/>
     </row>
     <row r="16">
@@ -1720,12 +1657,12 @@
           <t>Edit</t>
         </is>
       </c>
-      <c r="E54" s="23" t="inlineStr">
+      <c r="E54" s="24" t="inlineStr">
         <is>
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="F54" s="23" t="inlineStr">
+      <c r="F54" s="24" t="inlineStr">
         <is>
           <t>2026-10-03</t>
         </is>
@@ -2510,12 +2447,12 @@
           <t>Edit</t>
         </is>
       </c>
-      <c r="E127" s="23" t="inlineStr">
+      <c r="E127" s="24" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="F127" s="23" t="inlineStr">
+      <c r="F127" s="24" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
